--- a/docs/scrum_artifacts/sprint_backlog.xlsx
+++ b/docs/scrum_artifacts/sprint_backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MIGUEL ÁNGEL\Documents\Universidad de Nariño\Semestres\Quinto semestre\Ingenieria de software III\CambridgeAcademy\docs-ver2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MIGUEL ÁNGEL\Documents\Universidad de Nariño\Semestres\Quinto semestre\Ingenieria de software III\CambridgeAcademy\new_ver\sprint4\ca_v0.4.0\docs\scrum_artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68943A3-5CC7-4D53-8121-DDF200E4119D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BF5A4C-5BDE-4F0F-8EFB-368A00B84E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sprint1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="222">
   <si>
     <t>HISTORIA</t>
   </si>
@@ -187,6 +187,513 @@
   </si>
   <si>
     <t>Crear funcion de consulta de profesores.</t>
+  </si>
+  <si>
+    <t>HU-03</t>
+  </si>
+  <si>
+    <t>Crear función de modificación de estudiantes en el modelo.</t>
+  </si>
+  <si>
+    <t>Crear función de modificación de estudiantes en el servicio.</t>
+  </si>
+  <si>
+    <t>Ajustar GUI de estudiantes para cargar datos al seleccionar un estudiante.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_manager_gui.py</t>
+  </si>
+  <si>
+    <t>Ajustar formulario dinámico para pasar de registro a edición.</t>
+  </si>
+  <si>
+    <t>ca_program/views/admin_base_manager_gui.py</t>
+  </si>
+  <si>
+    <t>HU-04</t>
+  </si>
+  <si>
+    <t>Crear función de eliminación permanente de estudiantes en el modelo.</t>
+  </si>
+  <si>
+    <t>Crear función de eliminación permanente de estudiantes en el servicio.</t>
+  </si>
+  <si>
+    <t>Integrar botón de eliminación de estudiantes con confirmación previa.</t>
+  </si>
+  <si>
+    <t>Ajustar distribución visual de botones de edición, cancelación y eliminación.</t>
+  </si>
+  <si>
+    <t>HU-05</t>
+  </si>
+  <si>
+    <t>Verificar función de búsqueda de estudiantes por nombre.</t>
+  </si>
+  <si>
+    <t>Integrar búsqueda de estudiantes desde la tabla administrativa.</t>
+  </si>
+  <si>
+    <t>HU-08</t>
+  </si>
+  <si>
+    <t>Crear función de modificación de cursos en el modelo.</t>
+  </si>
+  <si>
+    <t>Stiven Mejía</t>
+  </si>
+  <si>
+    <t>Crear función de modificación de cursos en el servicio.</t>
+  </si>
+  <si>
+    <t>Ajustar GUI de cursos para cargar datos al seleccionar un curso.</t>
+  </si>
+  <si>
+    <t>ca_program/views/course_manager_gui.py</t>
+  </si>
+  <si>
+    <t>Integrar modo edición para cursos registrados.</t>
+  </si>
+  <si>
+    <t>HU-09</t>
+  </si>
+  <si>
+    <t>Crear función de eliminación permanente de cursos en el modelo.</t>
+  </si>
+  <si>
+    <t>Crear función de eliminación permanente de cursos en el servicio.</t>
+  </si>
+  <si>
+    <t>Integrar eliminación de cursos desde la GUI administrativa.</t>
+  </si>
+  <si>
+    <t>Agregar confirmación previa antes de eliminar cursos.</t>
+  </si>
+  <si>
+    <t>HU-10</t>
+  </si>
+  <si>
+    <t>Verificar función de búsqueda de cursos por nombre.</t>
+  </si>
+  <si>
+    <t>Integrar búsqueda de cursos desde la tabla administrativa.</t>
+  </si>
+  <si>
+    <t>HU-13</t>
+  </si>
+  <si>
+    <t>Crear función de modificación de profesores en el modelo.</t>
+  </si>
+  <si>
+    <t>Crear función de modificación de profesores en el servicio.</t>
+  </si>
+  <si>
+    <t>Ajustar GUI de profesores para cargar datos al seleccionar un profesor.</t>
+  </si>
+  <si>
+    <t>ca_program/views/professor_manager_gui.py</t>
+  </si>
+  <si>
+    <t>Integrar modo edición para profesores registrados.</t>
+  </si>
+  <si>
+    <t>HU-14</t>
+  </si>
+  <si>
+    <t>Crear función de eliminación permanente de profesores en el modelo.</t>
+  </si>
+  <si>
+    <t>Bloquear eliminación de profesores con cursos asignados.</t>
+  </si>
+  <si>
+    <t>Crear función de eliminación permanente de profesores en el servicio.</t>
+  </si>
+  <si>
+    <t>Integrar eliminación de profesores desde la GUI administrativa.</t>
+  </si>
+  <si>
+    <t>Agregar confirmación previa antes de eliminar profesores.</t>
+  </si>
+  <si>
+    <t>HU-15</t>
+  </si>
+  <si>
+    <t>Verificar función de búsqueda de profesores por nombre.</t>
+  </si>
+  <si>
+    <t>Integrar búsqueda de profesores desde la tabla administrativa.</t>
+  </si>
+  <si>
+    <t>HU-18</t>
+  </si>
+  <si>
+    <t>Diseñar GUI principal para estudiantes.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/student_gui.py</t>
+  </si>
+  <si>
+    <t>Crear componente para visualizar cursos disponibles.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/available_courses_widget.py</t>
+  </si>
+  <si>
+    <t>Crear tarjetas visuales para cursos.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/course_card_widget.py</t>
+  </si>
+  <si>
+    <t>Integrar redirección de login hacia panel de estudiante.</t>
+  </si>
+  <si>
+    <t>ca_program/views/login_gui.py</t>
+  </si>
+  <si>
+    <t>Mostrar cursos disponibles en formato de tarjetas.</t>
+  </si>
+  <si>
+    <t>HU-19</t>
+  </si>
+  <si>
+    <t>Crear la clase enrollment.</t>
+  </si>
+  <si>
+    <t>ca_program/entities/enrollment.py</t>
+  </si>
+  <si>
+    <t>Crear el modelo enrollment.</t>
+  </si>
+  <si>
+    <t>ca_program/models/enrollment_model.py</t>
+  </si>
+  <si>
+    <t>Crear servicio de consulta de cursos inscritos.</t>
+  </si>
+  <si>
+    <t>ca_program/services/enrollment_service.py</t>
+  </si>
+  <si>
+    <t>Crear GUI para cursos inscritos del estudiante.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/enrolled_courses_widget.py</t>
+  </si>
+  <si>
+    <t>Integrar sección “Mis cursos” en el panel de estudiante.</t>
+  </si>
+  <si>
+    <t>HU-20</t>
+  </si>
+  <si>
+    <t>Crear vista de detalle de curso.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/course_detail_widget.py</t>
+  </si>
+  <si>
+    <t>Conectar botón “Consultar” desde cursos disponibles.</t>
+  </si>
+  <si>
+    <t>Conectar botón “Consultar” desde cursos inscritos.</t>
+  </si>
+  <si>
+    <t>Integrar navegación hacia detalle de curso en GUI estudiante.</t>
+  </si>
+  <si>
+    <t>Diseñar vista amigable para mostrar todos los datos del curso.</t>
+  </si>
+  <si>
+    <t>HU-21</t>
+  </si>
+  <si>
+    <t>Crear la clase receipt.</t>
+  </si>
+  <si>
+    <t>ca_program/entities/receipt.py</t>
+  </si>
+  <si>
+    <t>Crear la clase payment.</t>
+  </si>
+  <si>
+    <t>ca_program/entities/payment.py</t>
+  </si>
+  <si>
+    <t>Crear modelo receipt.</t>
+  </si>
+  <si>
+    <t>ca_program/models/receipt_model.py</t>
+  </si>
+  <si>
+    <t>Crear modelo payment.</t>
+  </si>
+  <si>
+    <t>ca_program/models/payment_model.py</t>
+  </si>
+  <si>
+    <t>Extender modelo enrollment para crear inscripciones.</t>
+  </si>
+  <si>
+    <t>Crear flujo de solicitud de inscripción.</t>
+  </si>
+  <si>
+    <t>Crear generación automática de recibo pendiente.</t>
+  </si>
+  <si>
+    <t>Crear lógica de vencimiento de recibos a 10 días.</t>
+  </si>
+  <si>
+    <t>Crear pago simulado de recibo.</t>
+  </si>
+  <si>
+    <t>Crear diálogo de pago para estudiantes.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/payment_dialog.py</t>
+  </si>
+  <si>
+    <t>Integrar botón de inscripción en detalle del curso.</t>
+  </si>
+  <si>
+    <t>Integrar botón de pago en detalle del curso.</t>
+  </si>
+  <si>
+    <t>Actualizar tarjetas de cursos según estado de inscripción.</t>
+  </si>
+  <si>
+    <t>Refrescar cursos disponibles y cursos inscritos después del pago.</t>
+  </si>
+  <si>
+    <t>HU-22</t>
+  </si>
+  <si>
+    <t>Crear componente de historial de pagos del estudiante.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/payments_record.py</t>
+  </si>
+  <si>
+    <t>Consultar pagos realizados por estudiante.</t>
+  </si>
+  <si>
+    <t>Mostrar resumen de pagos del estudiante.</t>
+  </si>
+  <si>
+    <t>Integrar historial de pagos en panel de estudiante.</t>
+  </si>
+  <si>
+    <t>HU-16</t>
+  </si>
+  <si>
+    <t>Extender modelo payment para consultar todos los pagos.</t>
+  </si>
+  <si>
+    <t>Crear resumen financiero administrativo.</t>
+  </si>
+  <si>
+    <t>Crear GUI administrativa para consulta de pagos.</t>
+  </si>
+  <si>
+    <t>ca_program/views/admin_view/payments_gui.py</t>
+  </si>
+  <si>
+    <t>Integrar sección “Pagos” en panel administrativo.</t>
+  </si>
+  <si>
+    <t>ca_program/views/admin_view/admin_gui.py</t>
+  </si>
+  <si>
+    <t>Actualizar dashboard administrativo con tarjeta de pagos.</t>
+  </si>
+  <si>
+    <t>ca_program/views/admin_view/admin_dashboard_widget.py</t>
+  </si>
+  <si>
+    <t>HU-30</t>
+  </si>
+  <si>
+    <t>Modificar modelo user para actualizar contraseña.</t>
+  </si>
+  <si>
+    <t>Crear servicio de gestión de cuenta.</t>
+  </si>
+  <si>
+    <t>ca_program/services/account_service.py</t>
+  </si>
+  <si>
+    <t>Crear diálogo reutilizable para cambiar contraseña.</t>
+  </si>
+  <si>
+    <t>ca_program/views/change_password_dialog.py</t>
+  </si>
+  <si>
+    <t>Integrar cambio de contraseña en GUI estudiante.</t>
+  </si>
+  <si>
+    <t>Integrar cambio de contraseña en GUI administrador.</t>
+  </si>
+  <si>
+    <t>Ajustar flujo de sesión para identificar usuario autenticado.</t>
+  </si>
+  <si>
+    <t>HU-24</t>
+  </si>
+  <si>
+    <t>Crear método para obtener profesor por usuario autenticado.</t>
+  </si>
+  <si>
+    <t>Crear método para consultar cursos asignados por profesor.</t>
+  </si>
+  <si>
+    <t>Crear función de consulta de cursos asignados para profesores.</t>
+  </si>
+  <si>
+    <t>Diseñar GUI principal para profesores.</t>
+  </si>
+  <si>
+    <t>ca_program/views/professor_view/professor_gui.py</t>
+  </si>
+  <si>
+    <t>Conectar login con panel de profesores.</t>
+  </si>
+  <si>
+    <t>HU-25</t>
+  </si>
+  <si>
+    <t>Crear método para consultar detalle de curso asignado.</t>
+  </si>
+  <si>
+    <t>Crear función de consulta de detalle de curso asignado.</t>
+  </si>
+  <si>
+    <t>Diseñar vista de detalle de curso para profesores.</t>
+  </si>
+  <si>
+    <t>ca_program/views/professor_view/professor_course_detail_widget.py</t>
+  </si>
+  <si>
+    <t>Conectar tarjetas de cursos con vista de detalle.</t>
+  </si>
+  <si>
+    <t>HU-26</t>
+  </si>
+  <si>
+    <t>Crear clase grade.</t>
+  </si>
+  <si>
+    <t>ca_program/entities/grade.py</t>
+  </si>
+  <si>
+    <t>Crear modelo grade.</t>
+  </si>
+  <si>
+    <t>ca_program/models/grade_model.py</t>
+  </si>
+  <si>
+    <t>Crear consulta de matrículas confirmadas por curso y profesor.</t>
+  </si>
+  <si>
+    <t>Crear función de registro de notas.</t>
+  </si>
+  <si>
+    <t>ca_program/services/grade_service.py</t>
+  </si>
+  <si>
+    <t>Diseñar GUI de registro de notas para profesores.</t>
+  </si>
+  <si>
+    <t>ca_program/views/professor_view/grade_registration_widget.py</t>
+  </si>
+  <si>
+    <t>Conectar detalle de curso con registro de notas.</t>
+  </si>
+  <si>
+    <t>Integrar vista de registro de notas en GUI de profesores.</t>
+  </si>
+  <si>
+    <t>HU-27</t>
+  </si>
+  <si>
+    <t>Crear consulta de notas por curso asignado al profesor.</t>
+  </si>
+  <si>
+    <t>Crear función de consulta de registro de notas por curso.</t>
+  </si>
+  <si>
+    <t>Diseñar planilla digital de notas para profesores.</t>
+  </si>
+  <si>
+    <t>ca_program/views/professor_view/grade_record_widget.py</t>
+  </si>
+  <si>
+    <t>Conectar detalle de curso con consulta de notas.</t>
+  </si>
+  <si>
+    <t>Integrar planilla de notas en GUI de profesores.</t>
+  </si>
+  <si>
+    <t>HU-28</t>
+  </si>
+  <si>
+    <t>Crear método para actualizar notas registradas.</t>
+  </si>
+  <si>
+    <t>Crear función para modificar notas de estudiantes.</t>
+  </si>
+  <si>
+    <t>Diseñar diálogo de edición de notas.</t>
+  </si>
+  <si>
+    <t>ca_program/views/professor_view/grade_edit_dialog.py</t>
+  </si>
+  <si>
+    <t>Integrar edición de notas en la planilla del profesor.</t>
+  </si>
+  <si>
+    <t>HU-23</t>
+  </si>
+  <si>
+    <t>Crear método para obtener estudiante por usuario autenticado.</t>
+  </si>
+  <si>
+    <t>Crear consulta de notas por estudiante.</t>
+  </si>
+  <si>
+    <t>Crear función de consulta de registro de notas del estudiante.</t>
+  </si>
+  <si>
+    <t>Diseñar GUI de consulta de notas para estudiantes.</t>
+  </si>
+  <si>
+    <t>ca_program/views/student_view/student_grade_record_widget.py</t>
+  </si>
+  <si>
+    <t>Integrar sección “Mis notas” en GUI estudiantil.</t>
+  </si>
+  <si>
+    <t>HU-17</t>
+  </si>
+  <si>
+    <t>Crear búsqueda de estudiantes para consulta administrativa.</t>
+  </si>
+  <si>
+    <t>Crear consulta administrativa de notas por estudiante.</t>
+  </si>
+  <si>
+    <t>Crear función administrativa para consultar registro académico.</t>
+  </si>
+  <si>
+    <t>Diseñar GUI administrativa de registro académico.</t>
+  </si>
+  <si>
+    <t>ca_program/views/admin_view/admin_grade_record_widget.py</t>
+  </si>
+  <si>
+    <t>Integrar sección “Registro académico” en GUI administrativa.</t>
+  </si>
+  <si>
+    <t>Actualizar panel principal administrativo con acceso a registro académico.</t>
   </si>
 </sst>
 </file>
@@ -855,27 +1362,1638 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA69986-38FC-4155-A165-2DC9417C5AEE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="40.7109375" style="3"/>
+    <col min="5" max="16384" width="40.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DA1026-E326-413F-AEFB-9301A08C3809}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="40.7109375" style="3"/>
+    <col min="5" max="16384" width="40.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC3C4AB-E565-4D84-9EE6-3E38028D25A3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="40.7109375" style="3"/>
+    <col min="5" max="16384" width="40.7109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>